--- a/data/raw/patient_data_template.xlsx
+++ b/data/raw/patient_data_template.xlsx
@@ -618,10 +618,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -1585,20 +1585,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>302939</v>
+        <v>900001</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Corum</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>1962-08-10</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>AMC</t>
@@ -1712,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -1726,12 +1734,12 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>TL-26-LOVTO77643</t>
+          <t>TL-00-EXAMPLE00000</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Erin Cobain</t>
+          <t>Dr. Jane Doe</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
@@ -1756,7 +1764,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Erin Cobain Email</t>
+          <t>referring physician email</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
@@ -1870,7 +1878,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>0</v>
@@ -2112,10 +2120,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -2304,10 +2312,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
@@ -2471,10 +2479,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -2635,10 +2643,10 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
